--- a/docs/oc-mensuales/gas-licuado-de-petroleo/ene-2025.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/ene-2025.xlsx
@@ -677,7 +677,11 @@
           <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -1440,7 +1444,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1583,7 +1587,11 @@
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -1774,7 +1782,11 @@
           <t>Hospital de Melipilla</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -1900,7 +1912,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -2091,7 +2107,11 @@
           <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -2139,7 +2159,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2152,7 +2172,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -2343,7 +2367,11 @@
           <t>CORP CULTURAL DE LA COMUNA DE LA GRANJA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -2391,7 +2419,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2404,7 +2432,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -3177,7 +3209,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4675,7 +4707,11 @@
           <t>SERVICIO DE SALUD BIO BIO HOSPITAL SANTA BARBARA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -5451,7 +5487,11 @@
           <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -5769,7 +5809,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5837,7 +5877,11 @@
           <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -5960,7 +6004,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6093,7 +6137,11 @@
           <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -6411,7 +6459,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6609,7 +6657,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -7057,7 +7109,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7187,10 +7239,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -7511,7 +7567,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -7767,7 +7827,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -8140,7 +8204,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -8153,7 +8217,11 @@
           <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -8474,7 +8542,11 @@
           <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -8860,7 +8932,11 @@
           <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="I131" t="inlineStr">
         <is>
           <t>EMPRESAS GASCO S.A.</t>
@@ -9164,7 +9240,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -9434,7 +9510,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9892,7 +9968,11 @@
           <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I147" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -10148,7 +10228,11 @@
           <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -11246,7 +11330,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12029,7 +12113,11 @@
           <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I180" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -13000,7 +13088,11 @@
           <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I195" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -14223,7 +14315,11 @@
           <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="I214" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -14995,7 +15091,11 @@
           <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I226" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -15118,7 +15218,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15381,7 +15481,11 @@
           <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I232" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -15637,7 +15741,11 @@
           <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I236" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -15763,7 +15871,11 @@
           <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I238" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -16146,7 +16258,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -17306,7 +17418,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -17436,7 +17548,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -18034,7 +18146,11 @@
           <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LOTA</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr"/>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I273" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -18417,7 +18533,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18547,7 +18663,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18612,7 +18728,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -19265,7 +19381,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I292" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -19453,10 +19573,14 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr"/>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I295" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -19517,7 +19641,11 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr"/>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="I296" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -19575,7 +19703,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -20228,7 +20356,11 @@
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr"/>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I307" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -20354,7 +20486,11 @@
           <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr"/>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
       <c r="I309" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -20737,7 +20873,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20867,7 +21003,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -21907,7 +22043,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -22167,7 +22303,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -23076,7 +23212,11 @@
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr"/>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I351" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -23137,7 +23277,11 @@
           <t>Hospital de Melipilla</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr"/>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I352" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -23328,7 +23472,11 @@
           <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr"/>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I355" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -23451,7 +23599,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23776,7 +23924,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23831,7 +23979,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -23844,7 +23992,11 @@
           <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr"/>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I363" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -24035,7 +24187,11 @@
           <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr"/>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I366" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -24349,7 +24505,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -25649,7 +25805,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -26367,7 +26523,11 @@
           <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr"/>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I402" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -26620,10 +26780,14 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
-        </is>
-      </c>
-      <c r="H406" t="inlineStr"/>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
       <c r="I406" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -26944,7 +27108,11 @@
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr"/>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I411" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -27525,7 +27693,11 @@
           <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr"/>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I420" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -28756,7 +28928,11 @@
           <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr"/>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="I439" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -28869,7 +29045,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -29139,7 +29315,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -29655,10 +29831,14 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
-        </is>
-      </c>
-      <c r="H453" t="inlineStr"/>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I453" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -29719,7 +29899,11 @@
           <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I454" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -30102,7 +30286,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -30495,7 +30679,11 @@
           <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
-      <c r="H466" t="inlineStr"/>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I466" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -30553,7 +30741,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -31528,7 +31716,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -31986,7 +32174,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H489" t="inlineStr"/>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
       <c r="I489" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -32047,7 +32239,11 @@
           <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
-      <c r="H490" t="inlineStr"/>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I490" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -32173,7 +32369,11 @@
           <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr"/>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I492" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -32299,7 +32499,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H494" t="inlineStr"/>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I494" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -32616,7 +32820,11 @@
           <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
-      <c r="H499" t="inlineStr"/>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I499" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -32742,7 +32950,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H501" t="inlineStr"/>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I501" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -33388,7 +33600,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H511" t="inlineStr"/>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I511" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -33579,7 +33795,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H514" t="inlineStr"/>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I514" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -34160,7 +34380,11 @@
           <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr"/>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I523" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -34286,7 +34510,11 @@
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr"/>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I525" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -34344,7 +34572,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -34724,7 +34952,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
@@ -34864,7 +35092,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -34932,7 +35160,11 @@
           <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
-      <c r="H535" t="inlineStr"/>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I535" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -35058,7 +35290,11 @@
           <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
-      <c r="H537" t="inlineStr"/>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
       <c r="I537" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -36022,7 +36258,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -36090,7 +36326,11 @@
           <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
-      <c r="H553" t="inlineStr"/>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I553" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -36668,10 +36908,14 @@
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
-        </is>
-      </c>
-      <c r="H562" t="inlineStr"/>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I562" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -37109,7 +37353,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
@@ -37764,7 +38008,11 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H579" t="inlineStr"/>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
       <c r="I579" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -38861,7 +39109,11 @@
           <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
-      <c r="H596" t="inlineStr"/>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
       <c r="I596" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -38919,7 +39171,7 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -39244,7 +39496,7 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -40352,7 +40604,11 @@
           <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
-      <c r="H619" t="inlineStr"/>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I619" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -40738,7 +40994,11 @@
           <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE MULCHEN</t>
         </is>
       </c>
-      <c r="H625" t="inlineStr"/>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I625" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -41120,7 +41380,11 @@
           <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
-      <c r="H631" t="inlineStr"/>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I631" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -41506,7 +41770,11 @@
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
-      <c r="H637" t="inlineStr"/>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I637" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -41567,7 +41835,11 @@
           <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
-      <c r="H638" t="inlineStr"/>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
       <c r="I638" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -42850,7 +43122,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
@@ -43571,7 +43843,7 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -43769,7 +44041,11 @@
           <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
-      <c r="H672" t="inlineStr"/>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
       <c r="I672" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -44792,7 +45068,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
@@ -45000,7 +45276,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H691" t="inlineStr"/>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I691" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -45451,7 +45731,11 @@
           <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
-      <c r="H698" t="inlineStr"/>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
       <c r="I698" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -46419,7 +46703,7 @@
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
@@ -46617,7 +46901,11 @@
           <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
-      <c r="H716" t="inlineStr"/>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="I716" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -46739,7 +47027,11 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H718" t="inlineStr"/>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I718" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -48291,7 +48583,11 @@
           <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
-      <c r="H742" t="inlineStr"/>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I742" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -48417,7 +48713,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H744" t="inlineStr"/>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I744" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -48475,7 +48775,7 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -48540,7 +48840,7 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -48735,7 +49035,7 @@
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -48855,7 +49155,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
@@ -48998,7 +49298,11 @@
           <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
-      <c r="H753" t="inlineStr"/>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="I753" t="inlineStr">
         <is>
           <t>EMPRESAS LIPIGAS S A</t>
@@ -49904,7 +50208,11 @@
           <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
-      <c r="H767" t="inlineStr"/>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
       <c r="I767" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -50810,7 +51118,11 @@
           <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
-      <c r="H781" t="inlineStr"/>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="I781" t="inlineStr">
         <is>
           <t>ABASTIBLE S.A.</t>
@@ -52626,7 +52938,11 @@
           <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
-      <c r="H809" t="inlineStr"/>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I809" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -53337,7 +53653,11 @@
           <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
-      <c r="H820" t="inlineStr"/>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I820" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
@@ -53460,7 +53780,7 @@
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H822" t="inlineStr">
@@ -53525,7 +53845,7 @@
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H823" t="inlineStr">
@@ -53590,7 +53910,7 @@
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
@@ -53723,7 +54043,11 @@
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
-      <c r="H826" t="inlineStr"/>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I826" t="inlineStr">
         <is>
           <t>GASCO GLP S A</t>
